--- a/utils/monday_sprint_sprint_2025-25.xlsx
+++ b/utils/monday_sprint_sprint_2025-25.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="329">
   <si>
     <t>Ticket</t>
   </si>
@@ -210,6 +210,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -261,7 +264,7 @@
     <t>14/08/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Agosto</t>
@@ -393,7 +396,7 @@
     <t>Willian Gabriel Paixão dos Santos</t>
   </si>
   <si>
-    <t>11/03/2026</t>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>19909</t>
@@ -411,7 +414,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -495,7 +498,7 @@
     <t>26/09/2025</t>
   </si>
   <si>
-    <t>25/02/2026</t>
+    <t>20/02/2026</t>
   </si>
   <si>
     <t>Setembro</t>
@@ -639,7 +642,7 @@
     <t>24/10/2025</t>
   </si>
   <si>
-    <t>29/04/2026</t>
+    <t>24/04/2026</t>
   </si>
   <si>
     <t>35044</t>
@@ -720,6 +723,9 @@
     <t>Carlos Correia</t>
   </si>
   <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
     <t>34651</t>
   </si>
   <si>
@@ -771,7 +777,7 @@
     <t>15/10/2024</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>34720</t>
@@ -897,7 +903,7 @@
     <t>09/12/2025</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>Ajuste Calendário Horários exibidos</t>
@@ -1986,21 +1992,21 @@
         <v>64</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -2012,7 +2018,7 @@
         <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>17</v>
@@ -2021,13 +2027,13 @@
         <v>24</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>17</v>
@@ -2044,7 +2050,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -2056,10 +2062,10 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -2088,7 +2094,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -2100,10 +2106,10 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>24</v>
@@ -2132,7 +2138,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -2144,10 +2150,10 @@
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>19</v>
@@ -2176,7 +2182,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -2188,39 +2194,39 @@
         <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2232,10 +2238,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -2264,7 +2270,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2276,10 +2282,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -2308,7 +2314,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2320,10 +2326,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -2352,7 +2358,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2364,39 +2370,39 @@
         <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2408,10 +2414,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -2440,7 +2446,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2452,25 +2458,25 @@
         <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>51</v>
@@ -2479,12 +2485,12 @@
         <v>21</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2496,10 +2502,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>24</v>
@@ -2528,7 +2534,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2540,10 +2546,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2572,7 +2578,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2584,10 +2590,10 @@
         <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2599,7 +2605,7 @@
         <v>38</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>17</v>
@@ -2608,7 +2614,7 @@
         <v>40</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>59</v>
@@ -2616,22 +2622,22 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
@@ -2660,7 +2666,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2672,10 +2678,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2704,7 +2710,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2716,10 +2722,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2748,7 +2754,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2760,10 +2766,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2792,7 +2798,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2804,25 +2810,25 @@
         <v>34</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>20</v>
@@ -2831,12 +2837,12 @@
         <v>21</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2848,39 +2854,39 @@
         <v>34</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2892,10 +2898,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2924,7 +2930,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2936,10 +2942,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2968,7 +2974,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2980,10 +2986,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -3012,7 +3018,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3024,10 +3030,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -3056,7 +3062,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -3068,7 +3074,7 @@
         <v>34</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>17</v>
@@ -3077,13 +3083,13 @@
         <v>24</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>17</v>
@@ -3100,7 +3106,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3112,10 +3118,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -3144,7 +3150,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3156,39 +3162,39 @@
         <v>34</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3200,10 +3206,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -3232,7 +3238,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3244,10 +3250,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3276,7 +3282,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3288,25 +3294,25 @@
         <v>34</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>20</v>
@@ -3315,12 +3321,12 @@
         <v>21</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3332,7 +3338,7 @@
         <v>34</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>17</v>
@@ -3341,13 +3347,13 @@
         <v>24</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>17</v>
@@ -3364,7 +3370,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3376,10 +3382,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
@@ -3408,22 +3414,22 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3452,7 +3458,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3464,10 +3470,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3496,7 +3502,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3508,16 +3514,16 @@
         <v>34</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>38</v>
@@ -3526,7 +3532,7 @@
         <v>57</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>40</v>
@@ -3540,7 +3546,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3552,10 +3558,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3576,7 +3582,7 @@
         <v>40</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>17</v>
@@ -3584,7 +3590,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3596,10 +3602,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3628,7 +3634,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3640,39 +3646,39 @@
         <v>34</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3684,10 +3690,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>24</v>
@@ -3708,7 +3714,7 @@
         <v>20</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>17</v>
@@ -3716,7 +3722,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3728,10 +3734,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3760,7 +3766,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3772,7 +3778,7 @@
         <v>34</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>17</v>
@@ -3781,13 +3787,13 @@
         <v>24</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>17</v>
@@ -3804,7 +3810,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3816,10 +3822,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3848,7 +3854,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3860,10 +3866,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3884,7 +3890,7 @@
         <v>20</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>17</v>
@@ -3892,7 +3898,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3904,10 +3910,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3936,7 +3942,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3948,10 +3954,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3972,7 +3978,7 @@
         <v>20</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>17</v>
@@ -3980,7 +3986,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3992,7 +3998,7 @@
         <v>34</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>17</v>
@@ -4001,13 +4007,13 @@
         <v>24</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>17</v>
@@ -4024,7 +4030,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4036,39 +4042,39 @@
         <v>34</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4080,25 +4086,25 @@
         <v>34</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>40</v>
@@ -4112,7 +4118,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4124,10 +4130,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4156,7 +4162,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4168,39 +4174,39 @@
         <v>34</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4212,10 +4218,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>24</v>
@@ -4244,7 +4250,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4256,10 +4262,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4288,7 +4294,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4300,10 +4306,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>24</v>
@@ -4332,7 +4338,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4344,10 +4350,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4376,7 +4382,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4388,10 +4394,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4420,7 +4426,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4432,10 +4438,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4464,7 +4470,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4476,10 +4482,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4508,37 +4514,37 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>58</v>
+        <v>236</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>40</v>
@@ -4547,12 +4553,12 @@
         <v>25</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4564,10 +4570,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4608,10 +4614,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>24</v>
@@ -4640,7 +4646,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4652,10 +4658,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4684,7 +4690,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4696,10 +4702,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4728,7 +4734,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4740,10 +4746,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4772,7 +4778,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4784,10 +4790,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4816,7 +4822,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4828,10 +4834,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>24</v>
@@ -4860,7 +4866,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4872,31 +4878,31 @@
         <v>34</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>40</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>59</v>
@@ -4904,7 +4910,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4916,31 +4922,31 @@
         <v>34</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>46</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>59</v>
@@ -4948,7 +4954,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4960,31 +4966,31 @@
         <v>34</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>41</v>
@@ -4992,7 +4998,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5004,10 +5010,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>24</v>
@@ -5025,10 +5031,10 @@
         <v>17</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>17</v>
@@ -5036,7 +5042,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -5048,10 +5054,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -5080,7 +5086,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5092,39 +5098,39 @@
         <v>34</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M84" s="2" t="s">
         <v>25</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -5136,10 +5142,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>24</v>
@@ -5168,7 +5174,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5180,25 +5186,25 @@
         <v>34</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>20</v>
@@ -5207,12 +5213,12 @@
         <v>25</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5224,10 +5230,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5256,7 +5262,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5268,10 +5274,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5300,7 +5306,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5312,10 +5318,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5344,7 +5350,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5356,10 +5362,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5388,7 +5394,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5400,10 +5406,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
@@ -5432,7 +5438,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5444,10 +5450,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>19</v>
@@ -5476,7 +5482,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5488,22 +5494,22 @@
         <v>34</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>17</v>
@@ -5515,12 +5521,12 @@
         <v>21</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5529,42 +5535,42 @@
         <v>16</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>51</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5576,10 +5582,10 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -5608,7 +5614,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5620,39 +5626,39 @@
         <v>34</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5664,39 +5670,39 @@
         <v>34</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5708,39 +5714,39 @@
         <v>34</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -5752,39 +5758,39 @@
         <v>34</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -5796,34 +5802,34 @@
         <v>34</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -5839,23 +5845,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5863,16 +5869,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5891,7 +5897,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5912,7 +5918,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5943,12 +5949,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B2">
         <v>99</v>
@@ -5972,25 +5978,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6007,13 +6013,13 @@
         <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6028,7 +6034,7 @@
         <v>25</v>
       </c>
       <c r="Q10">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -6045,7 +6051,7 @@
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K11">
         <v>99</v>
@@ -6057,15 +6063,15 @@
         <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -6077,27 +6083,27 @@
         <v>71</v>
       </c>
       <c r="M12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="Q12">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -6109,15 +6115,15 @@
         <v>10</v>
       </c>
       <c r="P13" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="Q13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6128,10 +6134,16 @@
       <c r="N14">
         <v>8</v>
       </c>
+      <c r="P14" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -6139,7 +6151,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -6147,7 +6159,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6155,7 +6167,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6166,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6174,35 +6186,35 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -6211,7 +6223,7 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6222,7 +6234,7 @@
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>61</v>
@@ -6236,7 +6248,7 @@
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>35</v>
@@ -6244,72 +6256,72 @@
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-25.xlsx
+++ b/utils/monday_sprint_sprint_2025-25.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="316">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>35368</t>
+    <t>10660571946</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,256 +87,268 @@
     <t>28/11/2025</t>
   </si>
   <si>
+    <t>30/11/2025</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>10669227376</t>
+  </si>
+  <si>
+    <t>Nota técnica 2025.002 - Alteração no XML da nota</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
+  </si>
+  <si>
+    <t>04/12/2025</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>10660667356</t>
+  </si>
+  <si>
+    <t>Ajuste no sistema de inventário geral</t>
+  </si>
+  <si>
+    <t>10671126999</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Documentação API - FTFU</t>
+  </si>
+  <si>
+    <t>10671075841</t>
+  </si>
+  <si>
+    <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
+  </si>
+  <si>
+    <t>33048</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Custos FTF</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Precisamos automatizar um levantamento de custo de FTF por setor. A ideia é ter listado as operações trazendo o custo previsto de FTF e horas previstas de FTF de todos os modelos faturados do mês. Em anexo o Excel do exemplo de informação que precisa ser listada. Qualquer dúvida, est</t>
+  </si>
+  <si>
+    <t>Gabriel Lucas Kertichka</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>10669237622</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO TELA MODELO UNIVERSAL</t>
+  </si>
+  <si>
+    <t>10670752870</t>
+  </si>
+  <si>
+    <t>Siga - Consulta Sequencia (Alt c)</t>
+  </si>
+  <si>
+    <t>02/12/2025</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>10668918408</t>
+  </si>
+  <si>
+    <t>PENDÊNCIA NO PRÉ-PRODUTIVO</t>
+  </si>
+  <si>
+    <t>10660458551</t>
+  </si>
+  <si>
+    <t>Registro de solda digital</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>10669247960</t>
+  </si>
+  <si>
+    <t>Corrigir Cálculo do Custo de Bloqueios</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Melhorias APS</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>CRM - Nova carga inicial de oportunidades</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>34029</t>
-  </si>
-  <si>
-    <t>Nota técnica 2025.002 - Alteração no XML da nota</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>35357</t>
-  </si>
-  <si>
-    <t>Ajuste no sistema de inventário geral</t>
-  </si>
-  <si>
-    <t>10671126999</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Documentação API - FTFU</t>
-  </si>
-  <si>
-    <t>31699</t>
-  </si>
-  <si>
-    <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
-  </si>
-  <si>
-    <t>33048</t>
-  </si>
-  <si>
-    <t>Excelência Operacional</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Custos FTF</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Precisamos automatizar um levantamento de custo de FTF por setor. A ideia é ter listado as operações trazendo o custo previsto de FTF e horas previstas de FTF de todos os modelos faturados do mês. Em anexo o Excel do exemplo de informação que precisa ser listada. Qualquer dúvida, est</t>
-  </si>
-  <si>
-    <t>Gabriel Lucas Kertichka</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>25/07/2025</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>35125</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO TELA MODELO UNIVERSAL</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>Siga - Consulta Sequencia (Alt c)</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>35382</t>
-  </si>
-  <si>
-    <t>PENDÊNCIA NO PRÉ-PRODUTIVO</t>
-  </si>
-  <si>
-    <t>35399</t>
-  </si>
-  <si>
-    <t>Registro de solda digital</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>34931</t>
-  </si>
-  <si>
-    <t>Corrigir Cálculo do Custo de Bloqueios</t>
-  </si>
-  <si>
-    <t>Boa tarde Sandro. Código Descrição Matéria Prima 100579 SUCATA BLOQUEIO EA-16001 CF3 100587 SUCATA BLOQUEIO EA-16002 CF3M 100722 SUCATA BLOQUEIO EA-16007 CA6NM 100922 SUCATA BLOQUEIO EA-16019 102467 SUCATA BLOQUEIO EA-16020</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>10669237829</t>
+  </si>
+  <si>
+    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
+  </si>
+  <si>
+    <t>10669227302</t>
+  </si>
+  <si>
+    <t>Ordens de Compra - Benner</t>
+  </si>
+  <si>
+    <t>10660373913</t>
+  </si>
+  <si>
+    <t>REVISÃO E CRIAÇÃO DE NOVOS FLUXOS</t>
+  </si>
+  <si>
+    <t>10670398825</t>
+  </si>
+  <si>
+    <t>Melhoria nas informações da FTF/ OFERTA</t>
+  </si>
+  <si>
+    <t>10/12/2025</t>
+  </si>
+  <si>
+    <t>10660554516</t>
+  </si>
+  <si>
+    <t>Altona || Requisição Contas 39551 - 1.1.3.23.011 e 39549 - 1.1.3.15.002</t>
+  </si>
+  <si>
+    <t>03/12/2025</t>
+  </si>
+  <si>
+    <t>10660698944</t>
+  </si>
+  <si>
+    <t>IROG - Corte Pó de ferro BI</t>
+  </si>
+  <si>
+    <t>10660564401</t>
+  </si>
+  <si>
+    <t>Altona || OSI - Flag de suspensão</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
   </si>
   <si>
     <t>ADH</t>
   </si>
   <si>
-    <t>10/03/2026</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Melhorias APS</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>CRM - Nova carga inicial de oportunidades</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>35127</t>
-  </si>
-  <si>
-    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
-  </si>
-  <si>
-    <t>33395</t>
-  </si>
-  <si>
-    <t>Ordens de Compra - Benner</t>
-  </si>
-  <si>
-    <t>35434</t>
-  </si>
-  <si>
-    <t>REVISÃO E CRIAÇÃO DE NOVOS FLUXOS</t>
-  </si>
-  <si>
-    <t>33509</t>
-  </si>
-  <si>
-    <t>Melhoria nas informações da FTF/ OFERTA</t>
-  </si>
-  <si>
-    <t>35370</t>
-  </si>
-  <si>
-    <t>Altona || Requisição Contas 39551 - 1.1.3.23.011 e 39549 - 1.1.3.15.002</t>
-  </si>
-  <si>
-    <t>35323</t>
-  </si>
-  <si>
-    <t>IROG - Corte Pó de ferro BI</t>
-  </si>
-  <si>
-    <t>35369</t>
-  </si>
-  <si>
-    <t>Altona || OSI - Flag de suspensão</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>35318</t>
+    <t>10660716139</t>
   </si>
   <si>
     <t>Elaboração de um sistema de atividades para o laboratorio Químico</t>
   </si>
   <si>
-    <t>35423</t>
+    <t>10660404730</t>
   </si>
   <si>
     <t>Sistema de programação das moldagens - REUNIÃO</t>
   </si>
   <si>
-    <t>32037</t>
+    <t>11/12/2025</t>
+  </si>
+  <si>
+    <t>10668927399</t>
   </si>
   <si>
     <t>BI ajustagem</t>
   </si>
   <si>
-    <t>35333</t>
+    <t>10660669459</t>
   </si>
   <si>
     <t>Solicitação de Implementação de Nova Funcionalidade no WMS – “Pré-Transferência Aciaria”</t>
   </si>
   <si>
-    <t>34599</t>
+    <t>10669247959</t>
   </si>
   <si>
     <t>Sistema de Embalagens - Relatório Requisição Embalagem por Sequência</t>
   </si>
   <si>
-    <t>Bom dia Sandro. Cristian me passou que o desenvolvimento do sistema para gestão de Embalagem está concluído. Ótima notícia. Desenvolver relatório conforme layout no anexo. Relatório será de período fechado de mês, após o fechamento do mês. Listar mesmo as requisições que não tenham vinculadas etique</t>
-  </si>
-  <si>
-    <t>35440</t>
+    <t>10660359519</t>
   </si>
   <si>
     <t>Correção</t>
@@ -345,43 +357,31 @@
     <t>Apontamento - Corte pó de Ferro</t>
   </si>
   <si>
-    <t>35420</t>
+    <t>10660414131</t>
   </si>
   <si>
     <t>Alteração no sistema corridas</t>
   </si>
   <si>
-    <t>34507</t>
+    <t>10669227424</t>
   </si>
   <si>
     <t>Altona || Consignado - Conferência Fornecedores</t>
   </si>
   <si>
-    <t>35383</t>
+    <t>10660475675</t>
   </si>
   <si>
     <t>Ajuste na Tela “Materiais Endereçados”</t>
   </si>
   <si>
-    <t>35417</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
+    <t>10660408438</t>
   </si>
   <si>
     <t>MRP NO SETOR DE PRÉ-ANÁLISE (516)</t>
   </si>
   <si>
-    <t>Bom dia, Favor criar um formulário no setor 516 que possibilite a inclusão de informações no MRP do CPP, da mesma forma que existe no setor 509/527. Favor criar trava de movimentação do setor até que o formulário esteja respondido, portanto incluir opção de "SIM" ou "NÃO" antes do grid (Há necessida</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>19909</t>
+    <t>10669044147</t>
   </si>
   <si>
     <t>Registro de pintura</t>
@@ -390,25 +390,25 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>10669247968</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>35182</t>
+    <t>10668902509</t>
   </si>
   <si>
     <t>Pendência de Solda - 5530 x 5531</t>
   </si>
   <si>
-    <t>34921</t>
+    <t>10669302490</t>
   </si>
   <si>
     <t>HORIMETRO MANIULADORES</t>
   </si>
   <si>
-    <t>33412</t>
+    <t>10669116399</t>
   </si>
   <si>
     <t>Ajuste calculo Metas Gerais Irog</t>
@@ -417,31 +417,31 @@
     <t>CRM - Atualizar IDERP nos registros já existentes</t>
   </si>
   <si>
-    <t>35298</t>
+    <t>10660718766</t>
   </si>
   <si>
     <t>LISTA DE CPPs COM RADIOGRAFIA"</t>
   </si>
   <si>
-    <t>35206</t>
+    <t>10669297769</t>
   </si>
   <si>
     <t>Alterações nas etiquetas de moldagem</t>
   </si>
   <si>
-    <t>32677</t>
+    <t>10669044261</t>
   </si>
   <si>
     <t>PDI - Fixar colunas de identificação das cotas</t>
   </si>
   <si>
-    <t>35281</t>
+    <t>10660735354</t>
   </si>
   <si>
     <t>TELA DE ANEXOS DE MAPEAMENTO DIGITAL</t>
   </si>
   <si>
-    <t>34377</t>
+    <t>10669116342</t>
   </si>
   <si>
     <t>Lógica de ACR no sistema de manutenção - Pila 2 MP</t>
@@ -450,13 +450,13 @@
     <t>CRM - Produtos não estão não estão disponibilizado descrição</t>
   </si>
   <si>
-    <t>35273</t>
+    <t>10660746581</t>
   </si>
   <si>
     <t>Sistema retrabalho ajustagem com erro</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>10669118144</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -465,12 +465,15 @@
     <t>Inclusão dos novos pátios</t>
   </si>
   <si>
-    <t>35310</t>
+    <t>10660716882</t>
   </si>
   <si>
     <t>Apontamento jatos</t>
   </si>
   <si>
+    <t>07/12/2025</t>
+  </si>
+  <si>
     <t>34919</t>
   </si>
   <si>
@@ -492,7 +495,7 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>34427</t>
+    <t>18236204547</t>
   </si>
   <si>
     <t>ETFIC - Analise</t>
@@ -504,25 +507,25 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>35295</t>
+    <t>10660725501</t>
   </si>
   <si>
     <t>ROTEIRO PRELIMINAR NA TELA DE MOVIMENTAÇÃO DE AC</t>
   </si>
   <si>
-    <t>33387</t>
+    <t>10669297828</t>
   </si>
   <si>
     <t>HORIMETRO MANIPULADORES</t>
   </si>
   <si>
-    <t>34981</t>
+    <t>18321153361</t>
   </si>
   <si>
     <t>Criar aplicação no QSense - Exclusão de movimentação</t>
   </si>
   <si>
-    <t>34171</t>
+    <t>10669297967</t>
   </si>
   <si>
     <t>Contagem Proformas</t>
@@ -531,13 +534,13 @@
     <t>CRM - Nova Carga de clientes</t>
   </si>
   <si>
-    <t>33271</t>
+    <t>10669152970</t>
   </si>
   <si>
     <t>Alinhamento dos cálculos de disponibilidade (copy)</t>
   </si>
   <si>
-    <t>35253</t>
+    <t>18379250085</t>
   </si>
   <si>
     <t>Incluir Unidade de Negócio em Relatório</t>
@@ -549,13 +552,16 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>35403</t>
+    <t>10660444432</t>
   </si>
   <si>
     <t>Inclusão de Máquinas e Setor no MPO Acabamento</t>
   </si>
   <si>
-    <t>35208</t>
+    <t>08/12/2025</t>
+  </si>
+  <si>
+    <t>18379273043</t>
   </si>
   <si>
     <t>Criar campo novo ou relatório</t>
@@ -564,7 +570,7 @@
     <t>CRM - Testes unitários com usuário (oportunidade)</t>
   </si>
   <si>
-    <t>35272</t>
+    <t>10669304560</t>
   </si>
   <si>
     <t>Contagem de Inventário</t>
@@ -573,6 +579,9 @@
     <t>34896</t>
   </si>
   <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
     <t>Alteração de calculo do BI</t>
   </si>
   <si>
@@ -585,13 +594,13 @@
     <t>24/04/2026</t>
   </si>
   <si>
-    <t>35044</t>
+    <t>10660751492</t>
   </si>
   <si>
     <t>Registro de solda digital, IS NAO CADASTRADAS</t>
   </si>
   <si>
-    <t>35081</t>
+    <t>18379341493</t>
   </si>
   <si>
     <t>SUGESTÃO PARA MELHORIA NA H5000</t>
@@ -600,19 +609,19 @@
     <t>Fila</t>
   </si>
   <si>
-    <t>33401</t>
+    <t>10660787716</t>
   </si>
   <si>
     <t>Gráfico refugo diário - SENSE</t>
   </si>
   <si>
-    <t>33009</t>
+    <t>10669345785</t>
   </si>
   <si>
     <t>Ajustes Dalca e Lianco</t>
   </si>
   <si>
-    <t>33588</t>
+    <t>10669877474</t>
   </si>
   <si>
     <t>Indicador Cobertura de Estoques - Gerar Tabela</t>
@@ -624,186 +633,204 @@
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM (copy)</t>
   </si>
   <si>
-    <t>35246</t>
+    <t>10660747163</t>
   </si>
   <si>
     <t>Melhoria no sistema de coleta de assinatura digital</t>
   </si>
   <si>
-    <t>31270</t>
+    <t>10669161218</t>
   </si>
   <si>
     <t>MELHORIAS FLUXO 109 REVISÕES (copy)</t>
   </si>
   <si>
+    <t>10669053483</t>
+  </si>
+  <si>
     <t>PDI - Inspeção - Cotas informadas.</t>
   </si>
   <si>
-    <t>35067</t>
+    <t>10668903635</t>
+  </si>
+  <si>
+    <t>Erro IROG acabamento</t>
+  </si>
+  <si>
+    <t>10660766579</t>
+  </si>
+  <si>
+    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
+  </si>
+  <si>
+    <t>10669161449</t>
+  </si>
+  <si>
+    <t>Siga - Consulta Sequencia (Alt c) - Fluxo de movimentação</t>
+  </si>
+  <si>
+    <t>10669161115</t>
+  </si>
+  <si>
+    <t>Integração do mapeamento digital com sistema do PCP</t>
+  </si>
+  <si>
+    <t>10669170549</t>
+  </si>
+  <si>
+    <t>Ticket - Programação (copy)</t>
+  </si>
+  <si>
+    <t>10669212033</t>
+  </si>
+  <si>
+    <t>BI análise de ofertas - add metas</t>
+  </si>
+  <si>
+    <t>10669223959</t>
+  </si>
+  <si>
+    <t>Auditoria MPO, PID e Checklist</t>
+  </si>
+  <si>
+    <t>10669170776</t>
+  </si>
+  <si>
+    <t>Indicador Cobertura de Estoques</t>
+  </si>
+  <si>
+    <t>28392</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Notas de consignado - Medição NIMBI</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>34720</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação – Coleta de Assinatura Digital para Declaração de Recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde Gostaria de solicitar a implementação de uma funcionalidade para coleta de assinatura digital referente à Declaração de Recebimento de materiais. Contexto do Processo Atual Hoje, ao receber o romaneio/cópia da nota fiscal, realizamos a seguinte sequência: 1. Acessamos o sistema no menu Con</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>10669242771</t>
+  </si>
+  <si>
+    <t>[NIMBI] ATUALIZAÇÃO PARA ALTERAÇÃO DE PEDIDO - Entrega</t>
+  </si>
+  <si>
+    <t>10777724689</t>
+  </si>
+  <si>
+    <t>Indicador Cobertura de Estoques - Importar histórico de Planilhas</t>
+  </si>
+  <si>
+    <t>15/12/2025</t>
+  </si>
+  <si>
+    <t>10669247929</t>
+  </si>
+  <si>
+    <t>Cálculo de carga - Sistema de corridas</t>
+  </si>
+  <si>
+    <t>10680382040</t>
+  </si>
+  <si>
+    <t>Log de método dentro do sistema de baixa de preventivas e planejamento e programação</t>
+  </si>
+  <si>
+    <t>10682248571</t>
+  </si>
+  <si>
+    <t>Indicadores de Setup - IROG Usinagem (copy)</t>
+  </si>
+  <si>
+    <t>10692526136</t>
+  </si>
+  <si>
+    <t>Código visual de ACR - Tela TV Usinagem</t>
+  </si>
+  <si>
+    <t>10695315616</t>
+  </si>
+  <si>
+    <t>Permitir reprogramar horário já agendado (cliente pode solicitar reagendamento)</t>
+  </si>
+  <si>
+    <t>10695302777</t>
+  </si>
+  <si>
+    <t>Atualizar o calandario ao fechar o prompt de agendamento</t>
+  </si>
+  <si>
+    <t>10695307303</t>
+  </si>
+  <si>
+    <t>No prompt de agendamento, se teclar enter já inclui o registro, mas nao atualiza com as NFs selecionadas em seguida</t>
+  </si>
+  <si>
+    <t>10695318911</t>
+  </si>
+  <si>
+    <t>Nao etá trazendo informações de para o report da Ordem de coleta. Gerar numeração e infomações de modelo e QTD de peças</t>
+  </si>
+  <si>
+    <t>10695308160</t>
+  </si>
+  <si>
+    <t>Horario recusado nao deve ser apresentado no calendário</t>
+  </si>
+  <si>
+    <t>10695318663</t>
+  </si>
+  <si>
+    <t>Na lista de expedidor está apresentando nomes que nao são da expedição</t>
+  </si>
+  <si>
+    <t>35453</t>
+  </si>
+  <si>
+    <t>Qualidade</t>
+  </si>
+  <si>
+    <t>Inclusão de informação CPP</t>
+  </si>
+  <si>
+    <t>Boa tarde, Conforme conversa, por gentileza incluir campo para preencher o "Tempo de Enchimento Projetado" no Formulário de Projeto no CPP: E, além disso, esse novo dado deve aparecer no sistema de corridas, na tela abaixo (ao lado dessa informação deve aparecer a tolerância de +-15%): At.te,</t>
+  </si>
+  <si>
+    <t>Helena Mariana Segalla</t>
+  </si>
+  <si>
+    <t>35642</t>
   </si>
   <si>
     <t>Problema</t>
   </si>
   <si>
-    <t>Erro IROG acabamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Esta apresentando um erro no rateio de metas do IROG acabamento. At.te.,</t>
-  </si>
-  <si>
-    <t>Carlos Correia</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
-    <t>34651</t>
-  </si>
-  <si>
-    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
-  </si>
-  <si>
-    <t>Siga - Consulta Sequencia (Alt c) - Fluxo de movimentação</t>
-  </si>
-  <si>
-    <t>35257</t>
-  </si>
-  <si>
-    <t>Integração do mapeamento digital com sistema do PCP</t>
-  </si>
-  <si>
-    <t>33191</t>
-  </si>
-  <si>
-    <t>Ticket - Programação (copy)</t>
-  </si>
-  <si>
-    <t>34378</t>
-  </si>
-  <si>
-    <t>BI análise de ofertas - add metas</t>
-  </si>
-  <si>
-    <t>33360</t>
-  </si>
-  <si>
-    <t>Auditoria MPO, PID e Checklist</t>
-  </si>
-  <si>
-    <t>Indicador Cobertura de Estoques</t>
-  </si>
-  <si>
-    <t>28392</t>
-  </si>
-  <si>
-    <t>Notas de consignado - Medição NIMBI</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>34720</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação – Coleta de Assinatura Digital para Declaração de Recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde Gostaria de solicitar a implementação de uma funcionalidade para coleta de assinatura digital referente à Declaração de Recebimento de materiais. Contexto do Processo Atual Hoje, ao receber o romaneio/cópia da nota fiscal, realizamos a seguinte sequência: 1. Acessamos o sistema no menu Con</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>32839</t>
-  </si>
-  <si>
-    <t>[NIMBI] ATUALIZAÇÃO PARA ALTERAÇÃO DE PEDIDO - Entrega</t>
-  </si>
-  <si>
-    <t>Indicador Cobertura de Estoques - Importar histórico de Planilhas</t>
-  </si>
-  <si>
-    <t>15/12/2025</t>
-  </si>
-  <si>
-    <t>33632</t>
-  </si>
-  <si>
-    <t>Cálculo de carga - Sistema de corridas</t>
-  </si>
-  <si>
-    <t>35529</t>
-  </si>
-  <si>
-    <t>Log de método dentro do sistema de baixa de preventivas e planejamento e programação</t>
-  </si>
-  <si>
-    <t>02/12/2025</t>
-  </si>
-  <si>
-    <t>34534</t>
-  </si>
-  <si>
-    <t>Indicadores de Setup - IROG Usinagem (copy)</t>
-  </si>
-  <si>
-    <t>35557</t>
-  </si>
-  <si>
-    <t>Código visual de ACR - Tela TV Usinagem</t>
-  </si>
-  <si>
-    <t>03/12/2025</t>
-  </si>
-  <si>
-    <t>Permitir reprogramar horário já agendado (cliente pode solicitar reagendamento)</t>
-  </si>
-  <si>
-    <t>Atualizar o calandario ao fechar o prompt de agendamento</t>
-  </si>
-  <si>
-    <t>No prompt de agendamento, se teclar enter já inclui o registro, mas nao atualiza com as NFs selecionadas em seguida</t>
-  </si>
-  <si>
-    <t>Nao etá trazendo informações de para o report da Ordem de coleta. Gerar numeração e infomações de modelo e QTD de peças</t>
-  </si>
-  <si>
-    <t>Horario recusado nao deve ser apresentado no calendário</t>
-  </si>
-  <si>
-    <t>Na lista de expedidor está apresentando nomes que nao são da expedição</t>
-  </si>
-  <si>
-    <t>35453</t>
-  </si>
-  <si>
-    <t>Qualidade</t>
-  </si>
-  <si>
-    <t>Inclusão de informação CPP</t>
-  </si>
-  <si>
-    <t>Boa tarde, Conforme conversa, por gentileza incluir campo para preencher o "Tempo de Enchimento Projetado" no Formulário de Projeto no CPP: E, além disso, esse novo dado deve aparecer no sistema de corridas, na tela abaixo (ao lado dessa informação deve aparecer a tolerância de +-15%): At.te,</t>
-  </si>
-  <si>
-    <t>Helena Mariana Segalla</t>
-  </si>
-  <si>
-    <t>35642</t>
-  </si>
-  <si>
     <t>Rateio - Tempo Padrão de Modelos</t>
   </si>
   <si>
@@ -819,24 +846,42 @@
     <t>17/03/2026</t>
   </si>
   <si>
+    <t>10714920852</t>
+  </si>
+  <si>
     <t>Ajuste Calendário Horários exibidos</t>
   </si>
   <si>
     <t>05/12/2025</t>
   </si>
   <si>
+    <t>10766652057</t>
+  </si>
+  <si>
     <t>Criar Api para listar sequencias vivas em json- INVENTARIO</t>
   </si>
   <si>
+    <t>10766659385</t>
+  </si>
+  <si>
     <t>Criar API para sincronizar - INVENTARIO</t>
   </si>
   <si>
+    <t>10766656700</t>
+  </si>
+  <si>
     <t>Criar api para fazer login (obrigar login para sincronizar) - INVENTARIO</t>
   </si>
   <si>
+    <t>10766656106</t>
+  </si>
+  <si>
     <t>Alterações do front - INVENTARIO</t>
   </si>
   <si>
+    <t>10766675961</t>
+  </si>
+  <si>
     <t>Fotos no front - INVENTARIO</t>
   </si>
   <si>
@@ -846,7 +891,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-25</t>
+    <t>Jul/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1476,7 +1521,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1485,15 +1530,15 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1505,10 +1550,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1540,22 +1585,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1579,30 +1624,30 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1617,7 +1662,7 @@
         <v>32</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1626,51 +1671,51 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1711,7 +1756,7 @@
         <v>32</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1720,10 +1765,10 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1734,7 +1779,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
@@ -1758,24 +1803,24 @@
         <v>32</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1787,10 +1832,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1805,7 +1850,7 @@
         <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1814,15 +1859,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1834,10 +1879,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1852,10 +1897,10 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
@@ -1869,7 +1914,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1878,107 +1923,107 @@
         <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="I13" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1987,25 +2032,25 @@
         <v>77</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2040,19 +2085,19 @@
         <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2090,16 +2135,16 @@
         <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -2137,10 +2182,10 @@
         <v>24</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>27</v>
@@ -2181,24 +2226,24 @@
         <v>32</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2210,10 +2255,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2228,7 +2273,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -2245,7 +2290,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2257,10 +2302,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2275,7 +2320,7 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2292,7 +2337,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2304,10 +2349,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2322,7 +2367,7 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2339,37 +2384,37 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2378,15 +2423,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2398,10 +2443,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2419,10 +2464,10 @@
         <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>27</v>
@@ -2433,7 +2478,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2445,10 +2490,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2463,10 +2508,10 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2480,7 +2525,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2492,10 +2537,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2510,24 +2555,24 @@
         <v>32</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2539,10 +2584,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2557,13 +2602,13 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
@@ -2574,7 +2619,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2583,60 +2628,60 @@
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2651,7 +2696,7 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2668,7 +2713,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2680,10 +2725,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2698,7 +2743,7 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2715,7 +2760,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2727,10 +2772,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2745,7 +2790,7 @@
         <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2754,15 +2799,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2774,10 +2819,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2809,37 +2854,37 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2892,13 +2937,13 @@
         <v>124</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -2909,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
@@ -2936,16 +2981,16 @@
         <v>24</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -2980,19 +3025,19 @@
         <v>32</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3027,7 +3072,7 @@
         <v>32</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -3036,10 +3081,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -3083,30 +3128,30 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="C38" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>133</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>31</v>
@@ -3115,13 +3160,13 @@
         <v>77</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -3130,10 +3175,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -3168,7 +3213,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3224,10 +3269,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -3262,19 +3307,19 @@
         <v>32</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -3309,7 +3354,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3356,7 +3401,7 @@
         <v>32</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3365,30 +3410,30 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="C44" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>144</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3397,13 +3442,13 @@
         <v>77</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3412,10 +3457,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -3497,7 +3542,7 @@
         <v>32</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3506,10 +3551,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -3544,7 +3589,7 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3561,69 +3606,69 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>77</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3635,27 +3680,27 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3667,10 +3712,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3685,7 +3730,7 @@
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3702,7 +3747,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3714,10 +3759,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3732,7 +3777,7 @@
         <v>32</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3741,15 +3786,15 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3761,10 +3806,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>31</v>
@@ -3776,10 +3821,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3788,15 +3833,15 @@
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3808,10 +3853,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3826,39 +3871,39 @@
         <v>32</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>31</v>
@@ -3867,13 +3912,13 @@
         <v>77</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3882,15 +3927,15 @@
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3902,10 +3947,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3923,21 +3968,21 @@
         <v>24</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3949,10 +3994,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3964,7 +4009,7 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>24</v>
@@ -3976,7 +4021,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -3984,7 +4029,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3996,10 +4041,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -4014,7 +4059,7 @@
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -4031,7 +4076,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -4043,10 +4088,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -4058,7 +4103,7 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>24</v>
@@ -4070,7 +4115,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -4078,22 +4123,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>31</v>
@@ -4102,30 +4147,30 @@
         <v>77</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4137,10 +4182,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>31</v>
@@ -4155,7 +4200,7 @@
         <v>32</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4164,54 +4209,54 @@
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -4219,7 +4264,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4231,10 +4276,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4249,10 +4294,10 @@
         <v>23</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
@@ -4266,7 +4311,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -4278,10 +4323,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4293,19 +4338,19 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>28</v>
@@ -4313,7 +4358,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4325,10 +4370,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>31</v>
@@ -4360,22 +4405,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4399,15 +4444,15 @@
         <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4419,10 +4464,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>31</v>
@@ -4437,24 +4482,24 @@
         <v>32</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4466,10 +4511,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4487,21 +4532,21 @@
         <v>24</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4513,10 +4558,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4531,7 +4576,7 @@
         <v>23</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -4548,7 +4593,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4560,10 +4605,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4581,21 +4626,21 @@
         <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4607,10 +4652,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4625,66 +4670,66 @@
         <v>32</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>209</v>
+        <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>213</v>
+        <v>24</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
@@ -4722,10 +4767,10 @@
         <v>24</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>27</v>
@@ -4736,22 +4781,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>55</v>
+        <v>216</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>31</v>
@@ -4766,7 +4811,7 @@
         <v>32</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
@@ -4775,15 +4820,15 @@
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4795,10 +4840,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4816,21 +4861,21 @@
         <v>24</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4842,10 +4887,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4863,21 +4908,21 @@
         <v>24</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4889,10 +4934,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4916,15 +4961,15 @@
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4936,10 +4981,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4954,7 +4999,7 @@
         <v>32</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>25</v>
@@ -4963,15 +5008,15 @@
         <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
@@ -4983,10 +5028,10 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>31</v>
@@ -5001,118 +5046,118 @@
         <v>32</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
@@ -5124,10 +5169,10 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>31</v>
@@ -5151,15 +5196,15 @@
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5171,10 +5216,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>31</v>
@@ -5186,27 +5231,27 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5218,10 +5263,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5239,21 +5284,21 @@
         <v>24</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5265,10 +5310,10 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5280,27 +5325,27 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>245</v>
+        <v>57</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>124</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
@@ -5312,10 +5357,10 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>31</v>
@@ -5327,10 +5372,10 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>245</v>
+        <v>57</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
@@ -5339,15 +5384,15 @@
         <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5359,10 +5404,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5374,10 +5419,10 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -5386,15 +5431,15 @@
         <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>147</v>
+        <v>253</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
@@ -5406,10 +5451,10 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5421,10 +5466,10 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>25</v>
@@ -5433,15 +5478,15 @@
         <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
@@ -5453,10 +5498,10 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
@@ -5468,10 +5513,10 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>25</v>
@@ -5480,15 +5525,15 @@
         <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>147</v>
+        <v>257</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5500,10 +5545,10 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5515,10 +5560,10 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>25</v>
@@ -5527,15 +5572,15 @@
         <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>147</v>
+        <v>259</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5547,10 +5592,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5562,10 +5607,10 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>25</v>
@@ -5574,15 +5619,15 @@
         <v>26</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -5594,10 +5639,10 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5609,10 +5654,10 @@
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>25</v>
@@ -5621,15 +5666,15 @@
         <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>147</v>
+        <v>263</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
@@ -5641,10 +5686,10 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -5656,10 +5701,10 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>25</v>
@@ -5668,45 +5713,45 @@
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>25</v>
@@ -5723,7 +5768,7 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>16</v>
@@ -5732,45 +5777,45 @@
         <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>147</v>
+        <v>277</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
@@ -5782,10 +5827,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -5797,10 +5842,10 @@
         <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L95" s="2" t="s">
         <v>25</v>
@@ -5809,30 +5854,30 @@
         <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -5844,10 +5889,10 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>25</v>
@@ -5856,30 +5901,30 @@
         <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>183</v>
+        <v>282</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -5891,10 +5936,10 @@
         <v>22</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>25</v>
@@ -5903,30 +5948,30 @@
         <v>26</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>183</v>
+        <v>284</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
@@ -5938,10 +5983,10 @@
         <v>22</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>25</v>
@@ -5950,30 +5995,30 @@
         <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>183</v>
+        <v>286</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>20</v>
@@ -5985,10 +6030,10 @@
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>25</v>
@@ -5997,30 +6042,30 @@
         <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>183</v>
+        <v>288</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>20</v>
@@ -6032,10 +6077,10 @@
         <v>22</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>25</v>
@@ -6044,10 +6089,10 @@
         <v>26</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -6063,23 +6108,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6087,16 +6132,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6107,15 +6152,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>115.5</v>
+        <v>8.45</v>
       </c>
       <c r="J5" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6128,7 +6173,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K23">
         <v>8</v>
@@ -6136,7 +6181,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6167,12 +6212,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B2">
         <v>99</v>
@@ -6186,35 +6231,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>115.5</v>
+        <v>8.45</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6222,7 +6267,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6231,13 +6276,13 @@
         <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6249,21 +6294,21 @@
         <v>57</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q10">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>18</v>
@@ -6278,30 +6323,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="M11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N11">
         <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q11">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -6313,10 +6358,10 @@
         <v>71</v>
       </c>
       <c r="J12" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="K12">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>124</v>
@@ -6325,7 +6370,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q12">
         <v>2</v>
@@ -6333,7 +6378,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -6345,86 +6390,100 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N13">
         <v>10</v>
       </c>
       <c r="P13" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="Q13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>232</v>
+        <v>95</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N14">
         <v>8</v>
       </c>
-      <c r="P14" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="N15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
       <c r="M16" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="N16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="M17" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6432,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6440,142 +6499,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F21" s="2">
-        <v>155</v>
+        <v>313</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="F24" s="2">
-        <v>80</v>
+        <v>313</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>313</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
